--- a/docs/plantilla-importacion-entregas-mayo.xlsx
+++ b/docs/plantilla-importacion-entregas-mayo.xlsx
@@ -1,41 +1,560 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Enrique Arenas\Documents\Control de Entregas - Formatto\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F1B01C-6B5B-4D76-A633-F3E9CDDF8231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="29610" yWindow="-120" windowWidth="28110" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Carga Mayo" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="171">
+  <si>
+    <t>Periodo</t>
+  </si>
+  <si>
+    <t>Linea Negocio</t>
+  </si>
+  <si>
+    <t>Proyecto</t>
+  </si>
+  <si>
+    <t>Fecha Despacho</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Descripcion</t>
+  </si>
+  <si>
+    <t>Torre</t>
+  </si>
+  <si>
+    <t>Nucleo</t>
+  </si>
+  <si>
+    <t>Piso</t>
+  </si>
+  <si>
+    <t>Deptos/Casas</t>
+  </si>
+  <si>
+    <t>Observacion</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>Constructora</t>
+  </si>
+  <si>
+    <t>COCINA</t>
+  </si>
+  <si>
+    <t>Particulares</t>
+  </si>
+  <si>
+    <t>ADICIONAL</t>
+  </si>
+  <si>
+    <t>Retail</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>Arboleda</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>CLOSET</t>
+  </si>
+  <si>
+    <t>CLOSET - 1 DEPT</t>
+  </si>
+  <si>
+    <t>A07</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>407 Depto</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>507 Depto</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>607 Depto</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>707 Depto</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>807 Depto</t>
+  </si>
+  <si>
+    <t>Cachapoal</t>
+  </si>
+  <si>
+    <t>2026-05-05</t>
+  </si>
+  <si>
+    <t>COCINA - PISO 9</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Murales</t>
+  </si>
+  <si>
+    <t>Chicauma</t>
+  </si>
+  <si>
+    <t>COCINA - 5 CASAS</t>
+  </si>
+  <si>
+    <t>5 CASAS</t>
+  </si>
+  <si>
+    <t>Casas 56 - 58 - 59 - 60 - 61</t>
+  </si>
+  <si>
+    <t>PUERTAS CLOSET</t>
+  </si>
+  <si>
+    <t>PUERTAS CLOSET - 9 CASAS</t>
+  </si>
+  <si>
+    <t>9 CASAS</t>
+  </si>
+  <si>
+    <t>Casas 49 - 51 - 53 - 55 - 56 - 58 - 59 - 60 - 61</t>
+  </si>
+  <si>
+    <t>2026-05-14</t>
+  </si>
+  <si>
+    <t>CLOSET - 6  CASAS</t>
+  </si>
+  <si>
+    <t>6  CASAS</t>
+  </si>
+  <si>
+    <t>Casas 76 - 74 -72 -71 - 70 - 69</t>
+  </si>
+  <si>
+    <t>COCINA - 6 CASAS</t>
+  </si>
+  <si>
+    <t>6 CASAS</t>
+  </si>
+  <si>
+    <t>Casas 76 - 74 - 72 - 71 -70 - 69</t>
+  </si>
+  <si>
+    <t>2026-05-19</t>
+  </si>
+  <si>
+    <t>CLOSET - 7 CASAS</t>
+  </si>
+  <si>
+    <t>7 CASAS</t>
+  </si>
+  <si>
+    <t>Casas 68 - 67 - 66 - 65 - 64 - 63 - 62</t>
+  </si>
+  <si>
+    <t>COCINA - 7 CASAS</t>
+  </si>
+  <si>
+    <t>Jardines de Bellavista</t>
+  </si>
+  <si>
+    <t>CLOSET - PISO 3</t>
+  </si>
+  <si>
+    <t>TORRE C</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>CLOSET - PISO 4</t>
+  </si>
+  <si>
+    <t>CLOSET - PISO 5</t>
+  </si>
+  <si>
+    <t>TORRE E</t>
+  </si>
+  <si>
+    <t>CLOSET - PISO 1</t>
+  </si>
+  <si>
+    <t>TORRE D</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>CLOSET - PISO 2</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>COCINA - PISO 1</t>
+  </si>
+  <si>
+    <t>COCINA - PISO 2</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>COCINA - PISO 3</t>
+  </si>
+  <si>
+    <t>COCINA - PISO 4</t>
+  </si>
+  <si>
+    <t>COCINA - PISO 5</t>
+  </si>
+  <si>
+    <t>Los Abetos / chillan</t>
+  </si>
+  <si>
+    <t>ADICIONAL - 16 CUBIERTAS</t>
+  </si>
+  <si>
+    <t>16 CUBIERTAS</t>
+  </si>
+  <si>
+    <t>CUBIERTAS 16 UNIDADES</t>
+  </si>
+  <si>
+    <t>CLOSET - 42 DEPT</t>
+  </si>
+  <si>
+    <t>42 DPTS</t>
+  </si>
+  <si>
+    <t>CLOSET 42 DEPTS</t>
+  </si>
+  <si>
+    <t>COCINA - 32 DEPT</t>
+  </si>
+  <si>
+    <t>32 DPTS</t>
+  </si>
+  <si>
+    <t>CLOSET 32 DEPTS</t>
+  </si>
+  <si>
+    <t>VANITORIO</t>
+  </si>
+  <si>
+    <t>VANITORIO - 32 DEPT</t>
+  </si>
+  <si>
+    <t>Los Sauces</t>
+  </si>
+  <si>
+    <t>207 Depto</t>
+  </si>
+  <si>
+    <t>Magnolia</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>CLOSET - 1 CASA</t>
+  </si>
+  <si>
+    <t>1 CASA</t>
+  </si>
+  <si>
+    <t>TIPO DE CASA CE</t>
+  </si>
+  <si>
+    <t>COCINA - 1 CASA</t>
+  </si>
+  <si>
+    <t>2026-05-13</t>
+  </si>
+  <si>
+    <t>CLOSET - 3 CASA</t>
+  </si>
+  <si>
+    <t>3 CASA</t>
+  </si>
+  <si>
+    <t>TIPO 2  CE / 1 DE</t>
+  </si>
+  <si>
+    <t>COCINA - 3 CASA</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>CLOSET - 4 CASA</t>
+  </si>
+  <si>
+    <t>4 CASA</t>
+  </si>
+  <si>
+    <t>TIPO 2  CE / 2 DE</t>
+  </si>
+  <si>
+    <t>COCINA - 4 CASA</t>
+  </si>
+  <si>
+    <t>VM3</t>
+  </si>
+  <si>
+    <t>12 Depto</t>
+  </si>
+  <si>
+    <t>COCINA - PISO 6</t>
+  </si>
+  <si>
+    <t>COCINA - PISO 7</t>
+  </si>
+  <si>
+    <t>CLOSET - PISO 6</t>
+  </si>
+  <si>
+    <t>Viento Norte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADICIONAL ISLAS </t>
+  </si>
+  <si>
+    <t>TORRE A1</t>
+  </si>
+  <si>
+    <t>1 - 5</t>
+  </si>
+  <si>
+    <t>Islas (falta info )</t>
+  </si>
+  <si>
+    <t>TORRE A2</t>
+  </si>
+  <si>
+    <t>COCINA - TORRE B4</t>
+  </si>
+  <si>
+    <t>TORRE B4</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>Pendientes Nucleo H</t>
+  </si>
+  <si>
+    <t>CLOSET - TORRE B4</t>
+  </si>
+  <si>
+    <t>CLOSET - MDOIFICACION</t>
+  </si>
+  <si>
+    <t>TORRE B3</t>
+  </si>
+  <si>
+    <t>Nuclo I</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>Nuclo J</t>
+  </si>
+  <si>
+    <t>Vive Quinta</t>
+  </si>
+  <si>
+    <t>PIERNAS</t>
+  </si>
+  <si>
+    <t>PIERNAS - PISO 5-8</t>
+  </si>
+  <si>
+    <t>5-8</t>
+  </si>
+  <si>
+    <t>CLOSET TERMO - PISO 5-8</t>
+  </si>
+  <si>
+    <t>Closet INT/WCL  PISO 5-6 (SIN CANCHA)</t>
+  </si>
+  <si>
+    <t>2026-05-22</t>
+  </si>
+  <si>
+    <t>MULTIFRUTA S.A</t>
+  </si>
+  <si>
+    <t>ESCRITORIO BENCH – 1700X700X750 – HICKORY GRIS GRAFITO</t>
+  </si>
+  <si>
+    <t>En Corte | NV: 100090991</t>
+  </si>
+  <si>
+    <t>ESCRITORIO BENCH – 1400X700X750 – HICKORY GRIS GRAFITO</t>
+  </si>
+  <si>
+    <t>CAJONERA FAST MÓVIL 2C 1K - 450x500x670 – GRIS GRAFITO HICKORY</t>
+  </si>
+  <si>
+    <t>ESTANTE MILA 2P – 5R – 850X450X2000 – HICKORY GRIS SOMBRA</t>
+  </si>
+  <si>
+    <t>MUEBLE AEREO FAST – 1P CON PISTÓN – 1200X350X400 – HICKORY</t>
+  </si>
+  <si>
+    <t>ESTACIÓN DE TRABAJO BENCH (CUB700) - 1500X1500X750 – HICKORY GRIS GRAFITO</t>
+  </si>
+  <si>
+    <t>GABINETE BASE 2P – 3C 2E – 1190X500X620 – HICKORY GRIS SOMBRA</t>
+  </si>
+  <si>
+    <t>ECHAIRS BY MASLIAH LIMITADA</t>
+  </si>
+  <si>
+    <t>CUBIERTA CIRCULAR – 600X600X18 - HICKORY</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>En Enchape | NV: 100091031</t>
+  </si>
+  <si>
+    <t>CUBIERTA CIRCULAR – 600X600X18 - NEGRO</t>
+  </si>
+  <si>
+    <t>CUBIERTA RECTANGULAR – 1200X600X18 - NEGRO</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>VIGAHOME SPA</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>BIBLIOTECA MILA – 3C 1P 2E – 800x500x1460 – BLANCO HICKORY</t>
+  </si>
+  <si>
+    <t>Cubicado | NV: 100091034</t>
+  </si>
+  <si>
+    <t>ESCRITORIO BENCH DOBLE - 1200X1200X750MM – BLANCO / HICKORY</t>
+  </si>
+  <si>
+    <t>ESCRITORIO MILA ADMINISTRATIVO - 1500x600x750 - BLANCO - HICKORY</t>
+  </si>
+  <si>
+    <t>CHILEMAT SPA</t>
+  </si>
+  <si>
+    <t>ESTACIÓN DE TRABAJO - FAST 4C (DER) - 1500x1500x750 - BLANCO HICKORY</t>
+  </si>
+  <si>
+    <t>Cubicado | NV: 100091035</t>
+  </si>
+  <si>
+    <t>SODIMAC</t>
+  </si>
+  <si>
+    <t>ESTANTE ESCALA</t>
+  </si>
+  <si>
+    <t>Forecast</t>
+  </si>
+  <si>
+    <t>CONSTRUMART</t>
+  </si>
+  <si>
+    <t>REPISA LINEAL 600X300 NEGRO</t>
+  </si>
+  <si>
+    <t>REPISA LINEAL 600X300 BLANCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VANITORIO REVERSIBLE NOGAL LINCOLN </t>
+  </si>
+  <si>
+    <t>MUEBLE</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="166" formatCode="yyyy/mm/dd;@"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -64,15 +583,101 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="13">
+    <dxf>
+      <numFmt numFmtId="166" formatCode="yyyy/mm/dd;@"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1D5E05E-AA85-48FE-8C34-DBBA0CC06FEB}" name="Tabla1" displayName="Tabla1" ref="A1:K83" totalsRowShown="0" headerRowDxfId="1" dataDxfId="2">
+  <autoFilter ref="A1:K83" xr:uid="{B1D5E05E-AA85-48FE-8C34-DBBA0CC06FEB}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{D691D0D7-A653-456F-B88E-F0133DA01E92}" name="Periodo" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{F713F76F-9F6E-4883-A876-462993E85C0C}" name="Linea Negocio" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{88EBB5F2-3722-499A-94EF-26ACD693C8D8}" name="Proyecto" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{08B45763-DF3B-4747-8ED4-6E31799F2983}" name="Fecha Despacho" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{5776CA7F-B24E-4039-B1F6-1D49BB432FAB}" name="Tipo" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{E6AE8103-C7A7-4FAF-8017-F584CD9E958B}" name="Descripcion" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{74D0F99D-1F6F-4AC7-B349-8F82212B0ABB}" name="Torre" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{6193BD4A-79D6-4687-AAF7-60BADEB956BD}" name="Nucleo" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{6FB1FE85-915E-41CA-B1FD-4671E82D8401}" name="Piso" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{F98A1A95-DCDF-4F7B-B444-A285BDA7D211}" name="Deptos/Casas" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{D5044CA3-2EE0-4392-AC6F-AE42DFA79A51}" name="Observacion" dataDxfId="3"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -396,200 +1001,2577 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K83"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="28.83203125" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="32.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
-    <col min="11" max="11" width="30.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12.796875" customWidth="1"/>
+    <col min="2" max="2" width="18.796875" customWidth="1"/>
+    <col min="3" max="3" width="28.796875" customWidth="1"/>
+    <col min="4" max="4" width="16.796875" customWidth="1"/>
+    <col min="5" max="5" width="18.796875" customWidth="1"/>
+    <col min="6" max="6" width="32.796875" customWidth="1"/>
+    <col min="7" max="10" width="14.796875" customWidth="1"/>
+    <col min="11" max="11" width="37.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Periodo</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Linea Negocio</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Proyecto</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Fecha Despacho</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Tipo</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Descripcion</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Torre</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Nucleo</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Piso</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Deptos/Casas</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Observacion</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>2026-05</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Constructora</v>
-      </c>
-      <c r="C2" t="str">
-        <v>VIVE QUINTA</v>
-      </c>
-      <c r="D2" t="str">
-        <v>2026-05-08</v>
-      </c>
-      <c r="E2" t="str">
-        <v>COCINA</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Cocinas deptos piso 4</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Torre A</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Nucleo 1</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Piso 4</v>
-      </c>
-      <c r="J2">
+    <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K2" t="str">
-        <v>Prioridad cliente</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2026-05</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Particulares</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Cliente particular ejemplo</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="E3" t="str">
-        <v>ADICIONAL</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Mueble especial segun orden</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
-      <c r="J3">
+    </row>
+    <row r="2" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="1">
         <v>1</v>
       </c>
-      <c r="K3" t="str">
-        <v>No aplica torre/nucleo/piso</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>2026-05</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Retail</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Retail ejemplo</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E4" t="str">
-        <v>POST VENTA</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Producto retail ejemplo</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
-      <c r="J4">
+      <c r="K2" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="1">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="1">
+        <v>11</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="1">
         <v>5</v>
       </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2026-05</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Convenio Marco</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Convenio marco ejemplo</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E5" t="str">
-        <v>QUINCALLERIA</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Entrega por convenio</v>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v/>
-      </c>
-      <c r="J5">
+      <c r="K8" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J9" s="1">
+        <v>9</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" s="1">
+        <v>6</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J11" s="1">
+        <v>6</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J12" s="1">
+        <v>7</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J13" s="1">
+        <v>7</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J14" s="1">
+        <v>6</v>
+      </c>
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15" s="1">
+        <v>6</v>
+      </c>
+      <c r="K15" s="1"/>
+    </row>
+    <row r="16" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J16" s="1">
+        <v>6</v>
+      </c>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" s="1">
+        <v>6</v>
+      </c>
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J18" s="1">
+        <v>6</v>
+      </c>
+      <c r="K18" s="1"/>
+    </row>
+    <row r="19" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J19" s="1">
+        <v>6</v>
+      </c>
+      <c r="K19" s="1"/>
+    </row>
+    <row r="20" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J20" s="1">
+        <v>6</v>
+      </c>
+      <c r="K20" s="1"/>
+    </row>
+    <row r="21" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J21" s="1">
+        <v>6</v>
+      </c>
+      <c r="K21" s="1"/>
+    </row>
+    <row r="22" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J22" s="1">
+        <v>6</v>
+      </c>
+      <c r="K22" s="1"/>
+    </row>
+    <row r="23" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J23" s="1">
+        <v>6</v>
+      </c>
+      <c r="K23" s="1"/>
+    </row>
+    <row r="24" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J24" s="1">
+        <v>6</v>
+      </c>
+      <c r="K24" s="1"/>
+    </row>
+    <row r="25" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J25" s="1">
+        <v>6</v>
+      </c>
+      <c r="K25" s="1"/>
+    </row>
+    <row r="26" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J26" s="1">
+        <v>6</v>
+      </c>
+      <c r="K26" s="1"/>
+    </row>
+    <row r="27" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J27" s="1">
+        <v>6</v>
+      </c>
+      <c r="K27" s="1"/>
+    </row>
+    <row r="28" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J28" s="1">
+        <v>6</v>
+      </c>
+      <c r="K28" s="1"/>
+    </row>
+    <row r="29" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D29" s="2">
+        <v>46149</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J29" s="1">
+        <v>16</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D30" s="2">
+        <v>46149</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J30" s="1">
+        <v>42</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D31" s="2">
+        <v>46149</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J31" s="1">
+        <v>32</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J32" s="1">
+        <v>32</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="J34" s="1">
+        <v>1</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="J35" s="1">
+        <v>1</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J36" s="1">
         <v>3</v>
       </c>
-      <c r="K5" t="str">
-        <v/>
+      <c r="K36" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J37" s="1">
+        <v>3</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J38" s="1">
+        <v>3</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J39" s="1">
+        <v>3</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J40" s="1">
+        <v>4</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J41" s="1">
+        <v>4</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J42" s="1">
+        <v>12</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J43" s="1">
+        <v>12</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J44" s="1">
+        <v>12</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J45" s="1">
+        <v>12</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J46" s="1">
+        <v>12</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J47" s="1">
+        <v>12</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J48" s="1">
+        <v>12</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J49" s="1">
+        <v>12</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+    </row>
+    <row r="55" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D57" s="2">
+        <v>46153</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D58" s="2">
+        <v>46153</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1">
+        <v>4</v>
+      </c>
+      <c r="J59" s="1">
+        <v>12</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J60" s="1">
+        <v>88</v>
+      </c>
+      <c r="K60" s="1"/>
+    </row>
+    <row r="61" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J61" s="1">
+        <v>88</v>
+      </c>
+      <c r="K61" s="1"/>
+    </row>
+    <row r="62" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1">
+        <v>5</v>
+      </c>
+      <c r="J62" s="1">
+        <v>22</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1">
+        <v>6</v>
+      </c>
+      <c r="J63" s="1">
+        <v>22</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1">
+        <v>5</v>
+      </c>
+      <c r="J64" s="1">
+        <v>22</v>
+      </c>
+      <c r="K64" s="1"/>
+    </row>
+    <row r="65" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1">
+        <v>6</v>
+      </c>
+      <c r="J65" s="1">
+        <v>22</v>
+      </c>
+      <c r="K65" s="1"/>
+    </row>
+    <row r="66" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1">
+        <v>200</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1">
+        <v>100</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1">
+        <v>100</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A83" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1">
+        <v>100</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K5"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>